--- a/Matematika Diskrit/Tables of Light LED.xlsx
+++ b/Matematika Diskrit/Tables of Light LED.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\Documents\Important\Kuliah\Semester 2\Matematika Diskrit\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -392,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -481,6 +481,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2513,10 +2514,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:44">
-      <c r="C2" s="25">
-        <v>1</v>
-      </c>
-      <c r="D2" s="29">
+      <c r="C2" s="29">
+        <v>1</v>
+      </c>
+      <c r="D2" s="36">
         <v>2</v>
       </c>
       <c r="E2" s="26">
@@ -2644,7 +2645,7 @@
       <c r="D3" s="29">
         <v>5</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="25">
         <v>6</v>
       </c>
       <c r="G3" s="27">
@@ -2663,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="L3" s="27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="27">
         <v>0</v>
@@ -2678,16 +2679,16 @@
         <v>0</v>
       </c>
       <c r="Q3" s="27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="27">
         <v>1</v>
       </c>
       <c r="S3" s="27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" s="27">
         <v>1</v>
@@ -2696,25 +2697,25 @@
         <v>0</v>
       </c>
       <c r="W3" s="27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="27">
         <v>1</v>
       </c>
       <c r="Y3" s="27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="27">
         <v>1</v>
       </c>
       <c r="AA3" s="32" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AB3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="AC3" s="30">
-        <v>1</v>
+      <c r="AC3" s="16">
+        <v>0</v>
       </c>
       <c r="AD3" s="17">
         <v>0</v>
@@ -2766,10 +2767,10 @@
       <c r="C4" s="25">
         <v>7</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="25">
         <v>8</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="25">
         <v>9</v>
       </c>
       <c r="G4" s="27">
@@ -2885,7 +2886,7 @@
       <c r="D5" s="29">
         <v>11</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="25">
         <v>12</v>
       </c>
       <c r="G5" s="27">
@@ -2998,7 +2999,7 @@
       <c r="C6" s="25">
         <v>13</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="29">
         <v>14</v>
       </c>
       <c r="E6" s="25">
